--- a/5_Squared/data/raw/Book1.xlsx
+++ b/5_Squared/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAVIDEONORIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E284FCB5-D06A-4701-8AF9-DF0DAE3130B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED63865-5F0D-4EA4-9958-2BF01D7AFC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439C21F9-69C9-4B19-9543-2110E9B4F67A}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="22875" windowHeight="11295" xr2:uid="{439C21F9-69C9-4B19-9543-2110E9B4F67A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="507">
   <si>
     <t>A UN Equity</t>
   </si>
@@ -1551,9 +1551,6 @@
   </si>
   <si>
     <t>FCFY</t>
-  </si>
-  <si>
-    <t>INS_Ownership</t>
   </si>
   <si>
     <t>#N/A N/A</t>
@@ -1566,7 +1563,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1931,15 +1928,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D794B378-62D4-41BF-9574-A756947403B5}">
-  <dimension ref="A1:SJ3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:SJ2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.625" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:504">
+    <row r="1" spans="1:504" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>503</v>
       </c>
@@ -3453,7 +3450,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="2" spans="1:504">
+    <row r="2" spans="1:504" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>504</v>
       </c>
@@ -3614,7 +3611,7 @@
         <v>-1.1922754635885462</v>
       </c>
       <c r="BB2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BC2">
         <v>4.9387842366857218</v>
@@ -3641,7 +3638,7 @@
         <v>7.7073655103651619</v>
       </c>
       <c r="BK2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BL2">
         <v>6.5852406260782423</v>
@@ -3662,7 +3659,7 @@
         <v>6.5963183526251443</v>
       </c>
       <c r="BR2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BS2">
         <v>6.4260752209922476</v>
@@ -3674,7 +3671,7 @@
         <v>5.4592330887534741</v>
       </c>
       <c r="BV2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BW2">
         <v>-36.835777854779025</v>
@@ -3719,7 +3716,7 @@
         <v>8.5714243768895155</v>
       </c>
       <c r="CK2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CL2">
         <v>4.6191522857191059</v>
@@ -4031,7 +4028,7 @@
         <v>13.92897012829437</v>
       </c>
       <c r="GK2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="GL2">
         <v>2.1421837673446276</v>
@@ -4091,7 +4088,7 @@
         <v>2.2906430429568543</v>
       </c>
       <c r="HE2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="HF2">
         <v>2.0016059120885683</v>
@@ -4118,7 +4115,7 @@
         <v>5.3004891114625874</v>
       </c>
       <c r="HN2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="HO2">
         <v>6.1092146479801688</v>
@@ -4244,13 +4241,13 @@
         <v>3.3753863991399213</v>
       </c>
       <c r="JD2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="JE2">
         <v>4.0419984926528389</v>
       </c>
       <c r="JF2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="JG2">
         <v>2.788736012380276</v>
@@ -4424,7 +4421,7 @@
         <v>3.2651200339764563</v>
       </c>
       <c r="LL2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="LM2">
         <v>13.771449738646083</v>
@@ -4475,7 +4472,7 @@
         <v>8.1065607590152986</v>
       </c>
       <c r="MC2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="MD2">
         <v>-0.48259244051451133</v>
@@ -4574,7 +4571,7 @@
         <v>3.9211939506809479</v>
       </c>
       <c r="NJ2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="NK2">
         <v>5.1438807804024291</v>
@@ -4616,7 +4613,7 @@
         <v>13.034646129616398</v>
       </c>
       <c r="NX2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="NY2">
         <v>9.2069950831370697</v>
@@ -4631,7 +4628,7 @@
         <v>5.2374418123502524</v>
       </c>
       <c r="OC2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="OD2">
         <v>4.7909818880265824</v>
@@ -4715,7 +4712,7 @@
         <v>2.0164886412889507</v>
       </c>
       <c r="PE2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="PF2">
         <v>2.0428097003160737</v>
@@ -4763,7 +4760,7 @@
         <v>0.99191050966426086</v>
       </c>
       <c r="PU2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="PV2">
         <v>5.3306022333441598</v>
@@ -4853,13 +4850,13 @@
         <v>1.3950893933523789</v>
       </c>
       <c r="QY2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="QZ2">
         <v>4.0664729426856621</v>
       </c>
       <c r="RA2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="RB2">
         <v>5.5588907929293727</v>
@@ -4913,7 +4910,7 @@
         <v>-8.8536754102061561</v>
       </c>
       <c r="RS2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="RT2">
         <v>2.9307535947553935</v>
@@ -4965,1520 +4962,6 @@
       </c>
       <c r="SJ2">
         <v>4.4596830745588543</v>
-      </c>
-    </row>
-    <row r="3" spans="1:504">
-      <c r="A3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B3">
-        <v>0.31197549351155313</v>
-      </c>
-      <c r="C3">
-        <v>6.5384193598044843E-2</v>
-      </c>
-      <c r="D3">
-        <v>8.3289549811132305E-2</v>
-      </c>
-      <c r="E3">
-        <v>3.2455584797247603</v>
-      </c>
-      <c r="F3">
-        <v>0.49606966239621236</v>
-      </c>
-      <c r="G3">
-        <v>2.9900891869187274</v>
-      </c>
-      <c r="H3">
-        <v>8.0037795779276291E-2</v>
-      </c>
-      <c r="I3">
-        <v>0.19764773338617828</v>
-      </c>
-      <c r="J3">
-        <v>0.25357618656291769</v>
-      </c>
-      <c r="K3">
-        <v>0.76590740094904042</v>
-      </c>
-      <c r="L3">
-        <v>0.14019083516373254</v>
-      </c>
-      <c r="M3">
-        <v>0.21779715639810426</v>
-      </c>
-      <c r="N3">
-        <v>0.41643305857476454</v>
-      </c>
-      <c r="O3">
-        <v>0.100097378982164</v>
-      </c>
-      <c r="P3">
-        <v>0.54474261706646288</v>
-      </c>
-      <c r="Q3">
-        <v>0.67513902350932808</v>
-      </c>
-      <c r="R3">
-        <v>0.34053155576164218</v>
-      </c>
-      <c r="S3">
-        <v>0.72212872413695262</v>
-      </c>
-      <c r="T3">
-        <v>0.68443765585375327</v>
-      </c>
-      <c r="U3">
-        <v>2.1739616547367842</v>
-      </c>
-      <c r="V3">
-        <v>0.36838440407443734</v>
-      </c>
-      <c r="W3">
-        <v>0.75395754868716747</v>
-      </c>
-      <c r="X3">
-        <v>0.49463708051066552</v>
-      </c>
-      <c r="Y3">
-        <v>0.3795277477123582</v>
-      </c>
-      <c r="Z3">
-        <v>0.39750675993331236</v>
-      </c>
-      <c r="AA3">
-        <v>0.27367552603562806</v>
-      </c>
-      <c r="AB3">
-        <v>0.45476367615282282</v>
-      </c>
-      <c r="AC3">
-        <v>0.42569152739785232</v>
-      </c>
-      <c r="AD3">
-        <v>0.21131233060337315</v>
-      </c>
-      <c r="AE3">
-        <v>0.21333889141139953</v>
-      </c>
-      <c r="AF3">
-        <v>8.5235347730713382E-2</v>
-      </c>
-      <c r="AG3">
-        <v>8.2513481521706726</v>
-      </c>
-      <c r="AH3">
-        <v>17.259090851211823</v>
-      </c>
-      <c r="AI3">
-        <v>1.0944919731907614</v>
-      </c>
-      <c r="AJ3">
-        <v>0.77781426220915906</v>
-      </c>
-      <c r="AK3">
-        <v>0.4967330612891947</v>
-      </c>
-      <c r="AL3">
-        <v>0.40079832162618562</v>
-      </c>
-      <c r="AM3">
-        <v>0.53443840174420254</v>
-      </c>
-      <c r="AN3">
-        <v>15.410900115832792</v>
-      </c>
-      <c r="AO3">
-        <v>10.419523642491939</v>
-      </c>
-      <c r="AP3">
-        <v>1.2084622023009339</v>
-      </c>
-      <c r="AQ3">
-        <v>1.6508738583407772</v>
-      </c>
-      <c r="AR3">
-        <v>4.8111045320426289</v>
-      </c>
-      <c r="AS3">
-        <v>0.39183562463241706</v>
-      </c>
-      <c r="AT3">
-        <v>0.4488902644494176</v>
-      </c>
-      <c r="AU3">
-        <v>7.9980771619044891E-2</v>
-      </c>
-      <c r="AV3">
-        <v>0.70236383243086731</v>
-      </c>
-      <c r="AW3">
-        <v>0.17417451863990166</v>
-      </c>
-      <c r="AX3">
-        <v>4.9027679306169043</v>
-      </c>
-      <c r="AY3">
-        <v>0.11795533909882405</v>
-      </c>
-      <c r="AZ3">
-        <v>0.25250200314789029</v>
-      </c>
-      <c r="BA3">
-        <v>0.11277282275199366</v>
-      </c>
-      <c r="BB3">
-        <v>0.16138337270621717</v>
-      </c>
-      <c r="BC3">
-        <v>0.28566605590407596</v>
-      </c>
-      <c r="BD3">
-        <v>0.54075728155339808</v>
-      </c>
-      <c r="BE3">
-        <v>0.49898546840123675</v>
-      </c>
-      <c r="BF3">
-        <v>0.17563912288255534</v>
-      </c>
-      <c r="BG3">
-        <v>22.874133940096403</v>
-      </c>
-      <c r="BH3">
-        <v>3.0876564645300251</v>
-      </c>
-      <c r="BI3">
-        <v>0.84039413019852804</v>
-      </c>
-      <c r="BJ3">
-        <v>0.20814771607777405</v>
-      </c>
-      <c r="BK3">
-        <v>0.34394372045851146</v>
-      </c>
-      <c r="BL3">
-        <v>0.22545136526448892</v>
-      </c>
-      <c r="BM3">
-        <v>0.14608778455359622</v>
-      </c>
-      <c r="BN3">
-        <v>2.7927265560087191</v>
-      </c>
-      <c r="BO3">
-        <v>1.9688267084990176</v>
-      </c>
-      <c r="BP3">
-        <v>7.4063528235567944E-2</v>
-      </c>
-      <c r="BQ3">
-        <v>0.4250546214219087</v>
-      </c>
-      <c r="BR3">
-        <v>0.36226017852597425</v>
-      </c>
-      <c r="BS3">
-        <v>13.687637330356619</v>
-      </c>
-      <c r="BT3">
-        <v>0.19044615923740721</v>
-      </c>
-      <c r="BU3">
-        <v>0.9365086625804202</v>
-      </c>
-      <c r="BV3">
-        <v>0.23352939025689484</v>
-      </c>
-      <c r="BW3">
-        <v>0.29491959440216453</v>
-      </c>
-      <c r="BX3">
-        <v>0.66954347632949007</v>
-      </c>
-      <c r="BY3">
-        <v>0.24722458311377044</v>
-      </c>
-      <c r="BZ3">
-        <v>6.1777774479422831</v>
-      </c>
-      <c r="CA3">
-        <v>0.20131991567360641</v>
-      </c>
-      <c r="CB3">
-        <v>0.45650153041112207</v>
-      </c>
-      <c r="CC3">
-        <v>0.25173382046228204</v>
-      </c>
-      <c r="CD3">
-        <v>0.75919567086983064</v>
-      </c>
-      <c r="CE3">
-        <v>0.15323007477691675</v>
-      </c>
-      <c r="CF3">
-        <v>7.8855741376271178</v>
-      </c>
-      <c r="CG3">
-        <v>0.28920400687991504</v>
-      </c>
-      <c r="CH3">
-        <v>0.50370712965604481</v>
-      </c>
-      <c r="CI3">
-        <v>0.24058141797212956</v>
-      </c>
-      <c r="CJ3">
-        <v>0.53672324180315067</v>
-      </c>
-      <c r="CK3">
-        <v>0.91975538284196545</v>
-      </c>
-      <c r="CL3">
-        <v>0.23025562134602362</v>
-      </c>
-      <c r="CM3">
-        <v>0.81664968369796875</v>
-      </c>
-      <c r="CN3">
-        <v>0.26953131640534245</v>
-      </c>
-      <c r="CO3">
-        <v>0.41873877484884914</v>
-      </c>
-      <c r="CP3">
-        <v>1.0874981612238894</v>
-      </c>
-      <c r="CQ3">
-        <v>1.8243617219389066</v>
-      </c>
-      <c r="CR3">
-        <v>0.14616479611950875</v>
-      </c>
-      <c r="CS3">
-        <v>0.41507553929762087</v>
-      </c>
-      <c r="CT3">
-        <v>0.66155834100248501</v>
-      </c>
-      <c r="CU3">
-        <v>0.28425193012258304</v>
-      </c>
-      <c r="CV3">
-        <v>0.78759005330833376</v>
-      </c>
-      <c r="CW3">
-        <v>0.36846733460958048</v>
-      </c>
-      <c r="CX3">
-        <v>0.62553149902856131</v>
-      </c>
-      <c r="CY3">
-        <v>0.82049118736159721</v>
-      </c>
-      <c r="CZ3">
-        <v>0.53418084045928782</v>
-      </c>
-      <c r="DA3">
-        <v>0.85297209532366569</v>
-      </c>
-      <c r="DB3">
-        <v>1.1707625448739762</v>
-      </c>
-      <c r="DC3">
-        <v>1.0393789489653249</v>
-      </c>
-      <c r="DD3">
-        <v>0.1279473879341165</v>
-      </c>
-      <c r="DE3">
-        <v>0.36212607413637016</v>
-      </c>
-      <c r="DF3">
-        <v>0.23710342463977996</v>
-      </c>
-      <c r="DG3">
-        <v>3.7178381285607855</v>
-      </c>
-      <c r="DH3">
-        <v>12.453158443919348</v>
-      </c>
-      <c r="DI3">
-        <v>8.5307130094578234</v>
-      </c>
-      <c r="DJ3">
-        <v>1.5192209128483043</v>
-      </c>
-      <c r="DK3">
-        <v>0.14280778094047833</v>
-      </c>
-      <c r="DL3">
-        <v>1.3010514384148792</v>
-      </c>
-      <c r="DM3">
-        <v>2.6362707475622966</v>
-      </c>
-      <c r="DN3">
-        <v>1.469083146402349</v>
-      </c>
-      <c r="DO3">
-        <v>6.571305235357007E-2</v>
-      </c>
-      <c r="DP3">
-        <v>1.2890527385739599</v>
-      </c>
-      <c r="DQ3">
-        <v>0.24647752125909558</v>
-      </c>
-      <c r="DR3">
-        <v>0.95788012491447638</v>
-      </c>
-      <c r="DS3">
-        <v>1.567008665002706</v>
-      </c>
-      <c r="DT3">
-        <v>0.10636869784205606</v>
-      </c>
-      <c r="DU3">
-        <v>0.17604532262045663</v>
-      </c>
-      <c r="DV3">
-        <v>1.958845068807179</v>
-      </c>
-      <c r="DW3">
-        <v>0.72939798038218506</v>
-      </c>
-      <c r="DX3">
-        <v>0.46369018325276412</v>
-      </c>
-      <c r="DY3">
-        <v>0.13774041835687795</v>
-      </c>
-      <c r="DZ3">
-        <v>0.55134171460628023</v>
-      </c>
-      <c r="EA3">
-        <v>0.7032740935914582</v>
-      </c>
-      <c r="EB3">
-        <v>0.37763297144040736</v>
-      </c>
-      <c r="EC3">
-        <v>1.154451640478636</v>
-      </c>
-      <c r="ED3">
-        <v>0.15480514595495939</v>
-      </c>
-      <c r="EE3">
-        <v>0.82430996829869674</v>
-      </c>
-      <c r="EF3">
-        <v>6.9721491337089549</v>
-      </c>
-      <c r="EG3">
-        <v>0.43975789975326973</v>
-      </c>
-      <c r="EH3">
-        <v>0.62399207036188531</v>
-      </c>
-      <c r="EI3">
-        <v>2.157697838547977</v>
-      </c>
-      <c r="EJ3">
-        <v>8.746279207748854</v>
-      </c>
-      <c r="EK3">
-        <v>3.8161213872832368E-2</v>
-      </c>
-      <c r="EL3">
-        <v>0.10311033789521656</v>
-      </c>
-      <c r="EM3">
-        <v>0.21839175834233496</v>
-      </c>
-      <c r="EN3">
-        <v>0.34183244836044013</v>
-      </c>
-      <c r="EO3">
-        <v>0.707222544351233</v>
-      </c>
-      <c r="EP3">
-        <v>0.31599635002894022</v>
-      </c>
-      <c r="EQ3">
-        <v>0.60007275090183998</v>
-      </c>
-      <c r="ER3">
-        <v>0.33093210427030928</v>
-      </c>
-      <c r="ES3">
-        <v>0.42769530654752885</v>
-      </c>
-      <c r="ET3">
-        <v>0.17273791773778921</v>
-      </c>
-      <c r="EU3">
-        <v>2.7613952095808383</v>
-      </c>
-      <c r="EV3">
-        <v>0.79944521774193544</v>
-      </c>
-      <c r="EW3">
-        <v>0.55891003801854577</v>
-      </c>
-      <c r="EX3">
-        <v>0.14960298289296023</v>
-      </c>
-      <c r="EY3">
-        <v>0.24955312499999999</v>
-      </c>
-      <c r="EZ3">
-        <v>0.14949584529385102</v>
-      </c>
-      <c r="FA3">
-        <v>0.21524961785192084</v>
-      </c>
-      <c r="FB3">
-        <v>0.71166458801031007</v>
-      </c>
-      <c r="FC3">
-        <v>1.4565308621037556</v>
-      </c>
-      <c r="FD3">
-        <v>0.16512770050349956</v>
-      </c>
-      <c r="FE3">
-        <v>0.28838562905787851</v>
-      </c>
-      <c r="FF3">
-        <v>0.17738679783439137</v>
-      </c>
-      <c r="FG3">
-        <v>1.2711078655464978</v>
-      </c>
-      <c r="FH3">
-        <v>0.2837996459252668</v>
-      </c>
-      <c r="FI3">
-        <v>0.25539352036332352</v>
-      </c>
-      <c r="FJ3">
-        <v>3.698567112246276</v>
-      </c>
-      <c r="FK3">
-        <v>0.27929434278768506</v>
-      </c>
-      <c r="FL3">
-        <v>1.3151839863158794</v>
-      </c>
-      <c r="FM3">
-        <v>0.73482701506069448</v>
-      </c>
-      <c r="FN3">
-        <v>9.2091895290379302</v>
-      </c>
-      <c r="FO3">
-        <v>0.14296614137118685</v>
-      </c>
-      <c r="FP3">
-        <v>0.84394679468219791</v>
-      </c>
-      <c r="FQ3">
-        <v>0.18749937175454842</v>
-      </c>
-      <c r="FR3">
-        <v>0.27606913003339151</v>
-      </c>
-      <c r="FS3">
-        <v>1.3861170101403333</v>
-      </c>
-      <c r="FT3">
-        <v>0.25222120452823693</v>
-      </c>
-      <c r="FU3">
-        <v>7.4866872683653121E-2</v>
-      </c>
-      <c r="FV3">
-        <v>0.26407882252079157</v>
-      </c>
-      <c r="FW3">
-        <v>0.69959385919641193</v>
-      </c>
-      <c r="FX3">
-        <v>1.1593609682475383</v>
-      </c>
-      <c r="FY3">
-        <v>0.80951246508794961</v>
-      </c>
-      <c r="FZ3">
-        <v>0.38221854973035169</v>
-      </c>
-      <c r="GA3">
-        <v>0.70354120654142982</v>
-      </c>
-      <c r="GB3">
-        <v>0.1810715396023265</v>
-      </c>
-      <c r="GC3">
-        <v>0.59530643569936592</v>
-      </c>
-      <c r="GD3">
-        <v>0.44158202023436582</v>
-      </c>
-      <c r="GE3">
-        <v>8.5413345707009274</v>
-      </c>
-      <c r="GF3">
-        <v>0.20791870026001241</v>
-      </c>
-      <c r="GG3">
-        <v>0.77289214811160867</v>
-      </c>
-      <c r="GH3">
-        <v>3.0468675856678975</v>
-      </c>
-      <c r="GI3">
-        <v>0.14346509439959315</v>
-      </c>
-      <c r="GJ3">
-        <v>0.84878814086232124</v>
-      </c>
-      <c r="GK3">
-        <v>0.42928592240080338</v>
-      </c>
-      <c r="GL3">
-        <v>1.2119609938544367</v>
-      </c>
-      <c r="GM3">
-        <v>0.14596697317605256</v>
-      </c>
-      <c r="GN3">
-        <v>1.1994415375853476</v>
-      </c>
-      <c r="GO3">
-        <v>0.81509730918309509</v>
-      </c>
-      <c r="GP3">
-        <v>0.42475608278741228</v>
-      </c>
-      <c r="GQ3">
-        <v>15.831257308186952</v>
-      </c>
-      <c r="GR3">
-        <v>0.56129977600149683</v>
-      </c>
-      <c r="GS3">
-        <v>0.50504676100947588</v>
-      </c>
-      <c r="GT3">
-        <v>0.88412879693987656</v>
-      </c>
-      <c r="GU3">
-        <v>0.2215971976302365</v>
-      </c>
-      <c r="GV3">
-        <v>0.28823380723370584</v>
-      </c>
-      <c r="GW3">
-        <v>9.6604713704203551</v>
-      </c>
-      <c r="GX3">
-        <v>8.6827972448284885E-2</v>
-      </c>
-      <c r="GY3">
-        <v>0.10586448916201675</v>
-      </c>
-      <c r="GZ3">
-        <v>0.38665817071074904</v>
-      </c>
-      <c r="HA3">
-        <v>0.79280428672816494</v>
-      </c>
-      <c r="HB3">
-        <v>0.1729408055918534</v>
-      </c>
-      <c r="HC3">
-        <v>0.21607968601539945</v>
-      </c>
-      <c r="HD3">
-        <v>1.6885743243853562</v>
-      </c>
-      <c r="HE3">
-        <v>13.97573229128356</v>
-      </c>
-      <c r="HF3">
-        <v>0.11140472346272759</v>
-      </c>
-      <c r="HG3">
-        <v>0.4251675326925054</v>
-      </c>
-      <c r="HH3">
-        <v>0.74129666421699358</v>
-      </c>
-      <c r="HI3">
-        <v>14.7973253204995</v>
-      </c>
-      <c r="HJ3">
-        <v>0.4544229744679833</v>
-      </c>
-      <c r="HK3">
-        <v>6.2172398515190892</v>
-      </c>
-      <c r="HL3">
-        <v>0.50547070634612945</v>
-      </c>
-      <c r="HM3">
-        <v>0.59753221007379564</v>
-      </c>
-      <c r="HN3">
-        <v>0.94700600037307536</v>
-      </c>
-      <c r="HO3">
-        <v>1.1658769286886823</v>
-      </c>
-      <c r="HP3">
-        <v>5.6529789128503274E-2</v>
-      </c>
-      <c r="HQ3">
-        <v>0.42519495217194597</v>
-      </c>
-      <c r="HR3">
-        <v>0.89081184037077976</v>
-      </c>
-      <c r="HS3">
-        <v>1.977635966603225</v>
-      </c>
-      <c r="HT3">
-        <v>1.6357744342647917</v>
-      </c>
-      <c r="HU3">
-        <v>8.821570704999418E-2</v>
-      </c>
-      <c r="HV3">
-        <v>0.14719259312045102</v>
-      </c>
-      <c r="HW3">
-        <v>0.42924417421962024</v>
-      </c>
-      <c r="HX3">
-        <v>0.28203449083494814</v>
-      </c>
-      <c r="HY3">
-        <v>0.49810472597614103</v>
-      </c>
-      <c r="HZ3">
-        <v>1.6246969375985687</v>
-      </c>
-      <c r="IA3">
-        <v>1.5979405276546077</v>
-      </c>
-      <c r="IB3">
-        <v>0.49480404774800191</v>
-      </c>
-      <c r="IC3">
-        <v>0.38507031202973574</v>
-      </c>
-      <c r="ID3">
-        <v>0.29018987209975466</v>
-      </c>
-      <c r="IE3">
-        <v>1.038122652236581</v>
-      </c>
-      <c r="IF3">
-        <v>3.0174277658031068</v>
-      </c>
-      <c r="IG3">
-        <v>0.10993371902510321</v>
-      </c>
-      <c r="IH3">
-        <v>0.59755166654487213</v>
-      </c>
-      <c r="II3">
-        <v>0.99608639853599645</v>
-      </c>
-      <c r="IJ3">
-        <v>0.3015542352149666</v>
-      </c>
-      <c r="IK3">
-        <v>1.0316733704533667</v>
-      </c>
-      <c r="IL3">
-        <v>0.81483761233477958</v>
-      </c>
-      <c r="IM3">
-        <v>7.6885227387387386E-2</v>
-      </c>
-      <c r="IN3">
-        <v>2.1255417481106496</v>
-      </c>
-      <c r="IO3">
-        <v>0.50135373944367956</v>
-      </c>
-      <c r="IP3">
-        <v>0.35167377000446104</v>
-      </c>
-      <c r="IQ3">
-        <v>0.95720683559222153</v>
-      </c>
-      <c r="IR3">
-        <v>0.26074067177708887</v>
-      </c>
-      <c r="IS3">
-        <v>0.89976114336630664</v>
-      </c>
-      <c r="IT3">
-        <v>0.52525158378532721</v>
-      </c>
-      <c r="IU3">
-        <v>3.1887462776945279</v>
-      </c>
-      <c r="IV3">
-        <v>0.34176092990978485</v>
-      </c>
-      <c r="IW3">
-        <v>0.74561581053467663</v>
-      </c>
-      <c r="IX3">
-        <v>1.3706847446543835</v>
-      </c>
-      <c r="IY3">
-        <v>1.2309735277801972</v>
-      </c>
-      <c r="IZ3">
-        <v>2.3195483132298502</v>
-      </c>
-      <c r="JA3">
-        <v>0.24377421118826686</v>
-      </c>
-      <c r="JB3">
-        <v>0.5773994535203375</v>
-      </c>
-      <c r="JC3">
-        <v>3.7363018280645331E-2</v>
-      </c>
-      <c r="JD3">
-        <v>0.36087089529898037</v>
-      </c>
-      <c r="JE3">
-        <v>0.62859172158573196</v>
-      </c>
-      <c r="JF3">
-        <v>0.32910924363578292</v>
-      </c>
-      <c r="JG3">
-        <v>0.74574947712132467</v>
-      </c>
-      <c r="JH3">
-        <v>0.47841357860012079</v>
-      </c>
-      <c r="JI3">
-        <v>2.2551690319891753</v>
-      </c>
-      <c r="JJ3">
-        <v>23.534572843793889</v>
-      </c>
-      <c r="JK3">
-        <v>0.1841697274723329</v>
-      </c>
-      <c r="JL3">
-        <v>0.22633513134395267</v>
-      </c>
-      <c r="JM3">
-        <v>12.773889004254753</v>
-      </c>
-      <c r="JN3">
-        <v>0.21074703020864169</v>
-      </c>
-      <c r="JO3">
-        <v>0.29162411286644946</v>
-      </c>
-      <c r="JP3">
-        <v>5.545286111986443E-2</v>
-      </c>
-      <c r="JQ3">
-        <v>8.0802910805914401</v>
-      </c>
-      <c r="JR3">
-        <v>0.86415820383613928</v>
-      </c>
-      <c r="JS3">
-        <v>1.8246935567828118</v>
-      </c>
-      <c r="JT3">
-        <v>0.3256242207524272</v>
-      </c>
-      <c r="JU3">
-        <v>0.34298417947030752</v>
-      </c>
-      <c r="JV3">
-        <v>1.9158455428008752</v>
-      </c>
-      <c r="JW3">
-        <v>0.20400876422277178</v>
-      </c>
-      <c r="JX3">
-        <v>0.16367727709511309</v>
-      </c>
-      <c r="JY3">
-        <v>7.1040373356768646E-2</v>
-      </c>
-      <c r="JZ3">
-        <v>0.37447403173669835</v>
-      </c>
-      <c r="KA3">
-        <v>0.10141364301247771</v>
-      </c>
-      <c r="KB3">
-        <v>0.31802689612426938</v>
-      </c>
-      <c r="KC3">
-        <v>0.36557981994830202</v>
-      </c>
-      <c r="KD3">
-        <v>1.361962011568882</v>
-      </c>
-      <c r="KE3">
-        <v>0.14842299728222813</v>
-      </c>
-      <c r="KF3">
-        <v>1.4292027139996497</v>
-      </c>
-      <c r="KG3">
-        <v>0.37228962553931155</v>
-      </c>
-      <c r="KH3">
-        <v>2.5585887507724596</v>
-      </c>
-      <c r="KI3">
-        <v>6.024927396284116E-2</v>
-      </c>
-      <c r="KJ3">
-        <v>0.65278864894226729</v>
-      </c>
-      <c r="KK3">
-        <v>1.5201898100116007</v>
-      </c>
-      <c r="KL3">
-        <v>0.48244584791001888</v>
-      </c>
-      <c r="KM3">
-        <v>3.1743944878269738E-2</v>
-      </c>
-      <c r="KN3">
-        <v>2.0563520596966933</v>
-      </c>
-      <c r="KO3">
-        <v>4.3348407633431979E-2</v>
-      </c>
-      <c r="KP3">
-        <v>0.10778771560623107</v>
-      </c>
-      <c r="KQ3">
-        <v>0.21719356303331289</v>
-      </c>
-      <c r="KR3">
-        <v>8.191940866977962E-2</v>
-      </c>
-      <c r="KS3">
-        <v>0.32091733520802501</v>
-      </c>
-      <c r="KT3">
-        <v>0.12692469474363768</v>
-      </c>
-      <c r="KU3">
-        <v>3.3730753219441931</v>
-      </c>
-      <c r="KV3">
-        <v>0.18374916607680492</v>
-      </c>
-      <c r="KW3">
-        <v>0.81975260764639901</v>
-      </c>
-      <c r="KX3">
-        <v>0.11025170472754887</v>
-      </c>
-      <c r="KY3">
-        <v>0.38130079946174406</v>
-      </c>
-      <c r="KZ3">
-        <v>0.13443565337119848</v>
-      </c>
-      <c r="LA3">
-        <v>1.4165038268555437</v>
-      </c>
-      <c r="LB3">
-        <v>0.30485740269532507</v>
-      </c>
-      <c r="LC3">
-        <v>0.26609436669791764</v>
-      </c>
-      <c r="LD3">
-        <v>3.9212203265605274</v>
-      </c>
-      <c r="LE3">
-        <v>5.0251724888286303E-2</v>
-      </c>
-      <c r="LF3">
-        <v>2.7073908047665034</v>
-      </c>
-      <c r="LG3">
-        <v>9.8007142277303561E-2</v>
-      </c>
-      <c r="LH3">
-        <v>0.20220148785157374</v>
-      </c>
-      <c r="LI3">
-        <v>3.5854519564426854</v>
-      </c>
-      <c r="LJ3">
-        <v>3.4653385760317401E-2</v>
-      </c>
-      <c r="LK3">
-        <v>0.39165001095624807</v>
-      </c>
-      <c r="LL3">
-        <v>0.39283843321120826</v>
-      </c>
-      <c r="LM3">
-        <v>0.6869657352742059</v>
-      </c>
-      <c r="LN3">
-        <v>0.33801798255864007</v>
-      </c>
-      <c r="LO3">
-        <v>0.25270850788398846</v>
-      </c>
-      <c r="LP3">
-        <v>0.68152738167156046</v>
-      </c>
-      <c r="LQ3">
-        <v>0.67824071997254265</v>
-      </c>
-      <c r="LR3">
-        <v>0.46651345556758617</v>
-      </c>
-      <c r="LS3">
-        <v>8.8869807950192031E-2</v>
-      </c>
-      <c r="LT3">
-        <v>0.11786135159034962</v>
-      </c>
-      <c r="LU3">
-        <v>0.57581558926445742</v>
-      </c>
-      <c r="LV3">
-        <v>0.3430220701301393</v>
-      </c>
-      <c r="LW3">
-        <v>1.1113530000939995</v>
-      </c>
-      <c r="LX3">
-        <v>0.2393767037575675</v>
-      </c>
-      <c r="LY3">
-        <v>0.17548202676864244</v>
-      </c>
-      <c r="LZ3">
-        <v>0.68634020798639817</v>
-      </c>
-      <c r="MA3">
-        <v>4.0583092772028574E-2</v>
-      </c>
-      <c r="MB3">
-        <v>0.42737560963744059</v>
-      </c>
-      <c r="MC3">
-        <v>1.7698790940471363</v>
-      </c>
-      <c r="MD3">
-        <v>0.54665175792208598</v>
-      </c>
-      <c r="ME3">
-        <v>3.714218395061728</v>
-      </c>
-      <c r="MF3">
-        <v>4.9070428383254105</v>
-      </c>
-      <c r="MG3">
-        <v>8.3875853516566914E-2</v>
-      </c>
-      <c r="MH3">
-        <v>5.6165036058613803E-2</v>
-      </c>
-      <c r="MI3">
-        <v>0.12932219062038963</v>
-      </c>
-      <c r="MJ3">
-        <v>0.14612411605591438</v>
-      </c>
-      <c r="MK3">
-        <v>8.2021728616830174</v>
-      </c>
-      <c r="ML3">
-        <v>0.18816296896267221</v>
-      </c>
-      <c r="MM3">
-        <v>0.79925082015864723</v>
-      </c>
-      <c r="MN3">
-        <v>0.5342965657878207</v>
-      </c>
-      <c r="MO3">
-        <v>40.510363891224273</v>
-      </c>
-      <c r="MP3">
-        <v>0.78560454723806095</v>
-      </c>
-      <c r="MQ3">
-        <v>0.12991262031771905</v>
-      </c>
-      <c r="MR3">
-        <v>0.39710262954229314</v>
-      </c>
-      <c r="MS3">
-        <v>0.73787009803921566</v>
-      </c>
-      <c r="MT3">
-        <v>6.8284056593170721</v>
-      </c>
-      <c r="MU3">
-        <v>0.2879289071573331</v>
-      </c>
-      <c r="MV3">
-        <v>1.871000781525721</v>
-      </c>
-      <c r="MW3">
-        <v>0.25594831043946042</v>
-      </c>
-      <c r="MX3">
-        <v>0.19266934257716292</v>
-      </c>
-      <c r="MY3">
-        <v>0.21893131143402586</v>
-      </c>
-      <c r="MZ3">
-        <v>2.8296892810506236E-2</v>
-      </c>
-      <c r="NA3">
-        <v>0.75471591084653733</v>
-      </c>
-      <c r="NB3">
-        <v>6.0104115523186077E-2</v>
-      </c>
-      <c r="NC3">
-        <v>0.25300985003748044</v>
-      </c>
-      <c r="ND3">
-        <v>0.18259592842457206</v>
-      </c>
-      <c r="NE3">
-        <v>0.65900021660917374</v>
-      </c>
-      <c r="NF3">
-        <v>1.6592409345727137</v>
-      </c>
-      <c r="NG3">
-        <v>0.25902955704915381</v>
-      </c>
-      <c r="NH3">
-        <v>3.4398732080833669</v>
-      </c>
-      <c r="NI3">
-        <v>0.17036802682632268</v>
-      </c>
-      <c r="NJ3">
-        <v>0.41745450651001342</v>
-      </c>
-      <c r="NK3">
-        <v>0.9204285648298749</v>
-      </c>
-      <c r="NL3">
-        <v>0.29633994842248568</v>
-      </c>
-      <c r="NM3">
-        <v>0.44162235799411476</v>
-      </c>
-      <c r="NN3">
-        <v>3.2444379688712188</v>
-      </c>
-      <c r="NO3">
-        <v>0.13278267925595633</v>
-      </c>
-      <c r="NP3">
-        <v>0.17856322874670405</v>
-      </c>
-      <c r="NQ3">
-        <v>0.23349166666666665</v>
-      </c>
-      <c r="NR3">
-        <v>10.186835015703132</v>
-      </c>
-      <c r="NS3">
-        <v>0.23497441774566974</v>
-      </c>
-      <c r="NT3">
-        <v>0.22315370952528296</v>
-      </c>
-      <c r="NU3">
-        <v>0.28342777620443022</v>
-      </c>
-      <c r="NV3">
-        <v>0.68634080874538994</v>
-      </c>
-      <c r="NW3">
-        <v>0.10656943979049914</v>
-      </c>
-      <c r="NX3">
-        <v>0.13155409143136779</v>
-      </c>
-      <c r="NY3">
-        <v>8.8049295210871611E-2</v>
-      </c>
-      <c r="NZ3">
-        <v>0.40733187618448791</v>
-      </c>
-      <c r="OA3">
-        <v>0.68924989584848217</v>
-      </c>
-      <c r="OB3">
-        <v>1.985238112195352</v>
-      </c>
-      <c r="OC3">
-        <v>0.2949711465701424</v>
-      </c>
-      <c r="OD3">
-        <v>10.43210750364045</v>
-      </c>
-      <c r="OE3">
-        <v>3.0036586854943472</v>
-      </c>
-      <c r="OF3">
-        <v>0.51993981262836497</v>
-      </c>
-      <c r="OG3">
-        <v>0.19533716997202685</v>
-      </c>
-      <c r="OH3">
-        <v>1.4984526874474373</v>
-      </c>
-      <c r="OI3">
-        <v>0.35474387311457095</v>
-      </c>
-      <c r="OJ3">
-        <v>2.2043456257928322</v>
-      </c>
-      <c r="OK3">
-        <v>0.12040222794320039</v>
-      </c>
-      <c r="OL3">
-        <v>7.6420985026456667E-2</v>
-      </c>
-      <c r="OM3">
-        <v>0.45412970815709375</v>
-      </c>
-      <c r="ON3">
-        <v>0.79434601724571452</v>
-      </c>
-      <c r="OO3">
-        <v>0.15618727269375932</v>
-      </c>
-      <c r="OP3">
-        <v>5.7418630482590549</v>
-      </c>
-      <c r="OQ3">
-        <v>0.33446792417437904</v>
-      </c>
-      <c r="OR3">
-        <v>1.8017177395232742</v>
-      </c>
-      <c r="OS3">
-        <v>0.20009546122828556</v>
-      </c>
-      <c r="OT3">
-        <v>13.873001355577685</v>
-      </c>
-      <c r="OU3">
-        <v>2.1702167740418541</v>
-      </c>
-      <c r="OV3">
-        <v>0.54663194870016252</v>
-      </c>
-      <c r="OW3">
-        <v>0.42829997598688674</v>
-      </c>
-      <c r="OX3">
-        <v>0.12647252943788181</v>
-      </c>
-      <c r="OY3">
-        <v>0.16932786913593056</v>
-      </c>
-      <c r="OZ3">
-        <v>0.58313630017113649</v>
-      </c>
-      <c r="PA3">
-        <v>9.8822318954248353E-2</v>
-      </c>
-      <c r="PB3">
-        <v>4.9063829963104856E-2</v>
-      </c>
-      <c r="PC3">
-        <v>0.29045517498184809</v>
-      </c>
-      <c r="PD3">
-        <v>6.5590941342771796</v>
-      </c>
-      <c r="PE3">
-        <v>0.58558122213683439</v>
-      </c>
-      <c r="PF3">
-        <v>0.27901102887059431</v>
-      </c>
-      <c r="PG3">
-        <v>8.9081729288529671E-2</v>
-      </c>
-      <c r="PH3">
-        <v>0.52140633876308362</v>
-      </c>
-      <c r="PI3">
-        <v>0.2807536154486161</v>
-      </c>
-      <c r="PJ3">
-        <v>0.40904919480547119</v>
-      </c>
-      <c r="PK3">
-        <v>0.93237758859918818</v>
-      </c>
-      <c r="PL3">
-        <v>4.1172192959969811</v>
-      </c>
-      <c r="PM3">
-        <v>0.2349888869076229</v>
-      </c>
-      <c r="PN3">
-        <v>0.10807328056508746</v>
-      </c>
-      <c r="PO3">
-        <v>0.75527499450432423</v>
-      </c>
-      <c r="PP3">
-        <v>0.37082949968091261</v>
-      </c>
-      <c r="PQ3">
-        <v>0.95920096145521461</v>
-      </c>
-      <c r="PR3">
-        <v>0.2844580459472571</v>
-      </c>
-      <c r="PS3">
-        <v>0.1192485132106233</v>
-      </c>
-      <c r="PT3">
-        <v>0.2938813753545057</v>
-      </c>
-      <c r="PU3">
-        <v>0.1936530144063888</v>
-      </c>
-      <c r="PV3">
-        <v>0.31500564745141718</v>
-      </c>
-      <c r="PW3">
-        <v>0.13396607013085488</v>
-      </c>
-      <c r="PX3">
-        <v>1.0671859599924789</v>
-      </c>
-      <c r="PY3">
-        <v>0.13657158102551872</v>
-      </c>
-      <c r="PZ3">
-        <v>0.2932241407325592</v>
-      </c>
-      <c r="QA3">
-        <v>0.20461680945670643</v>
-      </c>
-      <c r="QB3">
-        <v>0.4960437450176377</v>
-      </c>
-      <c r="QC3">
-        <v>1.5295759882448063</v>
-      </c>
-      <c r="QD3">
-        <v>0.34162986743008783</v>
-      </c>
-      <c r="QE3">
-        <v>1.8927943222197712</v>
-      </c>
-      <c r="QF3">
-        <v>0.52216093339789182</v>
-      </c>
-      <c r="QG3">
-        <v>0.31722625079485878</v>
-      </c>
-      <c r="QH3">
-        <v>11.097733369985118</v>
-      </c>
-      <c r="QI3">
-        <v>1.9869345742191653</v>
-      </c>
-      <c r="QJ3">
-        <v>0.258032582334494</v>
-      </c>
-      <c r="QK3">
-        <v>2.3191468815926504</v>
-      </c>
-      <c r="QL3">
-        <v>2.482722066364071</v>
-      </c>
-      <c r="QM3">
-        <v>0.16071158159680002</v>
-      </c>
-      <c r="QN3">
-        <v>0.94094071645484245</v>
-      </c>
-      <c r="QO3">
-        <v>0.51027836676411065</v>
-      </c>
-      <c r="QP3">
-        <v>0.67087361487000918</v>
-      </c>
-      <c r="QQ3">
-        <v>0.14815088168013854</v>
-      </c>
-      <c r="QR3">
-        <v>0.47684282288204721</v>
-      </c>
-      <c r="QS3">
-        <v>5.838722464637339</v>
-      </c>
-      <c r="QT3">
-        <v>0.29606757288924324</v>
-      </c>
-      <c r="QU3">
-        <v>0.18117174013012136</v>
-      </c>
-      <c r="QV3">
-        <v>0.13199164743681024</v>
-      </c>
-      <c r="QW3">
-        <v>3.9682146297709837E-2</v>
-      </c>
-      <c r="QX3">
-        <v>0.56675160937265601</v>
-      </c>
-      <c r="QY3">
-        <v>0.22758469629931222</v>
-      </c>
-      <c r="QZ3">
-        <v>4.7001357449375232E-2</v>
-      </c>
-      <c r="RA3">
-        <v>0.29148265663114498</v>
-      </c>
-      <c r="RB3">
-        <v>0.57773828848442055</v>
-      </c>
-      <c r="RC3">
-        <v>0.14715259716417706</v>
-      </c>
-      <c r="RD3">
-        <v>0.18823768574763131</v>
-      </c>
-      <c r="RE3">
-        <v>0.26768371321549145</v>
-      </c>
-      <c r="RF3">
-        <v>0.90229713140676115</v>
-      </c>
-      <c r="RG3">
-        <v>0.208187322809291</v>
-      </c>
-      <c r="RH3">
-        <v>0.99441081476033988</v>
-      </c>
-      <c r="RI3">
-        <v>0.52178639641388469</v>
-      </c>
-      <c r="RJ3">
-        <v>0.66841061218888775</v>
-      </c>
-      <c r="RK3">
-        <v>3.3539046547821028E-2</v>
-      </c>
-      <c r="RL3">
-        <v>1.1460144431177617</v>
-      </c>
-      <c r="RM3">
-        <v>0.10162806580547344</v>
-      </c>
-      <c r="RN3">
-        <v>1.4880036194863797</v>
-      </c>
-      <c r="RO3">
-        <v>1.6053528571428572</v>
-      </c>
-      <c r="RP3">
-        <v>0.77240007680557254</v>
-      </c>
-      <c r="RQ3">
-        <v>0.17342805999074865</v>
-      </c>
-      <c r="RR3">
-        <v>4.0395148709606914E-2</v>
-      </c>
-      <c r="RS3">
-        <v>0.15965175452321662</v>
-      </c>
-      <c r="RT3">
-        <v>0.2077827168081782</v>
-      </c>
-      <c r="RU3">
-        <v>0.49566104187831483</v>
-      </c>
-      <c r="RV3">
-        <v>0.19916816696170522</v>
-      </c>
-      <c r="RW3">
-        <v>26.365450802676381</v>
-      </c>
-      <c r="RX3">
-        <v>0.96395062183418267</v>
-      </c>
-      <c r="RY3">
-        <v>0.61187579716934704</v>
-      </c>
-      <c r="RZ3">
-        <v>0.50377284377217824</v>
-      </c>
-      <c r="SA3">
-        <v>0.43274682376693741</v>
-      </c>
-      <c r="SB3">
-        <v>0.95988556173423734</v>
-      </c>
-      <c r="SC3">
-        <v>0.22160587811567925</v>
-      </c>
-      <c r="SD3">
-        <v>0.21331497879529021</v>
-      </c>
-      <c r="SE3">
-        <v>0.18432525271303038</v>
-      </c>
-      <c r="SF3">
-        <v>0.91764468014461054</v>
-      </c>
-      <c r="SG3">
-        <v>0.15795551208063083</v>
-      </c>
-      <c r="SH3">
-        <v>0.17788471367530104</v>
-      </c>
-      <c r="SI3">
-        <v>0.9583811903227577</v>
-      </c>
-      <c r="SJ3">
-        <v>8.8697366697328792E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6487,6 +4970,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003464D13C5E1E804898547381FA127FE4" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="99b22227e3928510855587220690b7d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="261be4a7-5fbc-4669-b0d2-5e4b43038116" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4068453de13beef72f8fa3f3981c9ed9" ns3:_="">
     <xsd:import namespace="261be4a7-5fbc-4669-b0d2-5e4b43038116"/>
@@ -6636,15 +5128,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6654,6 +5137,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C469F9BA-905F-49CB-AE16-227F3A175812}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E56F9BA7-146A-4CA7-AA6D-19B42FC3F959}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6667,14 +5158,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C469F9BA-905F-49CB-AE16-227F3A175812}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
